--- a/reports/pro-oil/pro-oil-refunds-report.xlsx
+++ b/reports/pro-oil/pro-oil-refunds-report.xlsx
@@ -4268,7 +4268,7 @@
     <x:t>C00670695</x:t>
   </x:si>
   <x:si>
-    <x:t>ROMNEY FOR UTAH INC</x:t>
+    <x:t>ROMNEY PAC</x:t>
   </x:si>
   <x:si>
     <x:t>ROONEY, FRANCIS</x:t>
@@ -25888,7 +25888,7 @@
         <x:v>289</x:v>
       </x:c>
       <x:c r="H107" s="1">
-        <x:v>5000</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:8">
@@ -33974,7 +33974,7 @@
         <x:v>954</x:v>
       </x:c>
       <x:c r="H418" s="1">
-        <x:v>14000</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="419" spans="1:8">

--- a/reports/pro-oil/pro-oil-refunds-report.xlsx
+++ b/reports/pro-oil/pro-oil-refunds-report.xlsx
@@ -30503,7 +30503,7 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="H269" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="270" spans="1:8">

--- a/reports/pro-oil/pro-oil-refunds-report.xlsx
+++ b/reports/pro-oil/pro-oil-refunds-report.xlsx
@@ -1664,7 +1664,7 @@
     <x:t>C00039503</x:t>
   </x:si>
   <x:si>
-    <x:t>SHELL EMPLOYEE POLITICAL AWARENESS COMMITTEE</x:t>
+    <x:t>SHELL USA, INC. EMPLOYEE POLITICAL AWARENESS COMMITTEE</x:t>
   </x:si>
   <x:si>
     <x:t>C00310318</x:t>
@@ -30827,7 +30827,7 @@
         <x:v>672</x:v>
       </x:c>
       <x:c r="H279" s="1">
-        <x:v>3000</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="280" spans="1:8">
